--- a/materials/テスト.xlsx
+++ b/materials/テスト.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kouta\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e236ba606bb2c49d/デスクトップ/team10/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76A9E3D6-F396-4A0C-AEFF-E71AFDECE91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{76A9E3D6-F396-4A0C-AEFF-E71AFDECE91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EF7EE79-1DFA-4777-BFB0-8424FDB86E55}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{3ABCC1DB-D2CC-472C-80FA-CBA2E225551A}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{3ABCC1DB-D2CC-472C-80FA-CBA2E225551A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -122,168 +120,183 @@
     <t>EN-01</t>
   </si>
   <si>
+    <t>ゲームを開始する</t>
+  </si>
+  <si>
+    <t>左上付近にプレイヤー、左下・右上・右下にそれぞれ異なる敵（計3体）が配置されること</t>
+  </si>
+  <si>
+    <t>EN-02</t>
+  </si>
+  <si>
+    <t>プレイヤーの追跡</t>
+  </si>
+  <si>
+    <t>敵から離れた位置にプレイヤーが待機する</t>
+  </si>
+  <si>
+    <t>敵がプレイヤーの方向へ向かって移動しようとすること</t>
+  </si>
+  <si>
+    <t>EN-03</t>
+  </si>
+  <si>
+    <t>ブロック破壊のための爆弾設置</t>
+  </si>
+  <si>
+    <t>EN-04</t>
+  </si>
+  <si>
+    <t>プレイヤーの爆弾回避</t>
+  </si>
+  <si>
+    <t>プレイヤーが置いた爆弾の隣に敵が近づく</t>
+  </si>
+  <si>
+    <t>敵が爆弾のあるマスや危険なマスを避け、別の安全な方向へ迂回すること</t>
+  </si>
+  <si>
+    <t>EN-05</t>
+  </si>
+  <si>
+    <t>EN-06</t>
+  </si>
+  <si>
+    <t>他人の爆風による巻き込み死亡</t>
+  </si>
+  <si>
+    <t>ある敵が置いた爆弾（またはプレイヤーの爆弾）の爆風に、別の敵が巻き込まれる</t>
+  </si>
+  <si>
+    <t>EN-07</t>
+  </si>
+  <si>
+    <t>行き詰まり時の方向転換</t>
+  </si>
+  <si>
+    <t>一定時間で別のランダムな方向に向きを変えて動き出すこと</t>
+  </si>
+  <si>
+    <t>IT-01</t>
+  </si>
+  <si>
+    <t>アイテム出現</t>
+  </si>
+  <si>
+    <t>爆風でブロックが壊れたとき、確率でアイテムが出現する</t>
+  </si>
+  <si>
+    <t>ブロックが消えたマスにアイテム（火力・爆弾数・スピードアップ等）が出現すること</t>
+  </si>
+  <si>
+    <t>IT-02</t>
+  </si>
+  <si>
+    <t>アイテム取得</t>
+  </si>
+  <si>
+    <t>プレイヤーがアイテムに重なる</t>
+  </si>
+  <si>
+    <t>アイテムが回収され、対応する効果が即座に適用されること</t>
+  </si>
+  <si>
+    <t>IT-03</t>
+  </si>
+  <si>
+    <t>効果発揮（火力アップ）</t>
+  </si>
+  <si>
+    <t>火力アップアイテムを取得する</t>
+  </si>
+  <si>
+    <t>爆弾の爆風の届く範囲（マス数）が広がること</t>
+  </si>
+  <si>
+    <t>ST-01</t>
+  </si>
+  <si>
+    <t>ブロックの破壊</t>
+  </si>
+  <si>
+    <t>爆弾の爆風が破壊可能なブロック（ソフトブロック）に当たる</t>
+  </si>
+  <si>
+    <t>ブロックが消滅して通行可能になること</t>
+  </si>
+  <si>
+    <t>ST-02</t>
+  </si>
+  <si>
+    <t>爆弾の連鎖爆発</t>
+  </si>
+  <si>
+    <t>複数の爆弾の爆風が、別の爆弾に重なる</t>
+  </si>
+  <si>
+    <t>連鎖して他の爆弾も即座に爆発すること</t>
+  </si>
+  <si>
+    <t>ST-03</t>
+  </si>
+  <si>
+    <t>画面端の挙動</t>
+  </si>
+  <si>
+    <t>ステージの最外周（壁）に向かって移動・爆弾設置を行う</t>
+  </si>
+  <si>
+    <t>キャラクターが壁の外に出たり、ゲームがクラッシュしたりしないこと</t>
+  </si>
+  <si>
     <t>複数体の初期配置</t>
-  </si>
-  <si>
-    <t>ゲームを開始する</t>
-  </si>
-  <si>
-    <t>左上付近にプレイヤー、左下・右上・右下にそれぞれ異なる敵（計3体）が配置されること</t>
-  </si>
-  <si>
-    <t>EN-02</t>
-  </si>
-  <si>
-    <t>プレイヤーの追跡</t>
-  </si>
-  <si>
-    <t>敵から離れた位置にプレイヤーが待機する</t>
-  </si>
-  <si>
-    <t>敵がプレイヤーの方向へ向かって移動しようとすること</t>
-  </si>
-  <si>
-    <t>EN-03</t>
-  </si>
-  <si>
-    <t>ブロック破壊のための爆弾設置</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>敵の進行方向の1マス先に破壊可能なブロックがある</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>敵が足を止めて、その場所に爆弾を設置すること</t>
-  </si>
-  <si>
-    <t>EN-04</t>
-  </si>
-  <si>
-    <t>プレイヤーの爆弾回避</t>
-  </si>
-  <si>
-    <t>プレイヤーが置いた爆弾の隣に敵が近づく</t>
-  </si>
-  <si>
-    <t>敵が爆弾のあるマスや危険なマスを避け、別の安全な方向へ迂回すること</t>
-  </si>
-  <si>
-    <t>EN-05</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>自爆（自分の爆弾によるダメージ）</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>敵が自分で置いた爆弾の爆風範囲内に留まる</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>爆発した際、その敵自身も爆風ダメージを受けて消滅（死亡）すること</t>
-  </si>
-  <si>
-    <t>EN-06</t>
-  </si>
-  <si>
-    <t>他人の爆風による巻き込み死亡</t>
-  </si>
-  <si>
-    <t>ある敵が置いた爆弾（またはプレイヤーの爆弾）の爆風に、別の敵が巻き込まれる</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>巻き込まれた敵も正しくダメージを受けて消滅すること</t>
-  </si>
-  <si>
-    <t>EN-07</t>
-  </si>
-  <si>
-    <t>行き詰まり時の方向転換</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>敵が壁やブロック、他のオブジェクトに挟まれて移動できなくなる</t>
-  </si>
-  <si>
-    <t>一定時間で別のランダムな方向に向きを変えて動き出すこと</t>
-  </si>
-  <si>
-    <t>IT-01</t>
-  </si>
-  <si>
-    <t>アイテム出現</t>
-  </si>
-  <si>
-    <t>爆風でブロックが壊れたとき、確率でアイテムが出現する</t>
-  </si>
-  <si>
-    <t>ブロックが消えたマスにアイテム（火力・爆弾数・スピードアップ等）が出現すること</t>
-  </si>
-  <si>
-    <t>IT-02</t>
-  </si>
-  <si>
-    <t>アイテム取得</t>
-  </si>
-  <si>
-    <t>プレイヤーがアイテムに重なる</t>
-  </si>
-  <si>
-    <t>アイテムが回収され、対応する効果が即座に適用されること</t>
-  </si>
-  <si>
-    <t>IT-03</t>
-  </si>
-  <si>
-    <t>効果発揮（火力アップ）</t>
-  </si>
-  <si>
-    <t>火力アップアイテムを取得する</t>
-  </si>
-  <si>
-    <t>爆弾の爆風の届く範囲（マス数）が広がること</t>
-  </si>
-  <si>
-    <t>ST-01</t>
-  </si>
-  <si>
-    <t>ブロックの破壊</t>
-  </si>
-  <si>
-    <t>爆弾の爆風が破壊可能なブロック（ソフトブロック）に当たる</t>
-  </si>
-  <si>
-    <t>ブロックが消滅して通行可能になること</t>
-  </si>
-  <si>
-    <t>ST-02</t>
-  </si>
-  <si>
-    <t>爆弾の連鎖爆発</t>
-  </si>
-  <si>
-    <t>複数の爆弾の爆風が、別の爆弾に重なる</t>
-  </si>
-  <si>
-    <t>連鎖して他の爆弾も即座に爆発すること</t>
-  </si>
-  <si>
-    <t>ST-03</t>
-  </si>
-  <si>
-    <t>画面端の挙動</t>
-  </si>
-  <si>
-    <t>ステージの最外周（壁）に向かって移動・爆弾設置を行う</t>
-  </si>
-  <si>
-    <t>キャラクターが壁の外に出たり、ゲームがクラッシュしたりしないこと</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -646,14 +659,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{321151BE-422D-4EB6-B2A8-3D9E0DD9EA6C}">
   <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="29.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="70.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="74.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="70.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="74.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -670,7 +683,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -687,7 +700,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -704,7 +717,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -721,7 +734,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -738,7 +751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -755,228 +768,230 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>26</v>
       </c>
       <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
         <v>27</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>28</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
         <v>29</v>
       </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>30</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>31</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>32</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
         <v>33</v>
       </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>34</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
         <v>35</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B10" t="s">
         <v>36</v>
       </c>
-      <c r="D9" t="s">
+      <c r="C10" t="s">
         <v>37</v>
       </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="D10" t="s">
         <v>38</v>
       </c>
-      <c r="B10" t="s">
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
         <v>39</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
         <v>40</v>
       </c>
-      <c r="D10" t="s">
+      <c r="B12" t="s">
         <v>41</v>
       </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+      <c r="C12" t="s">
         <v>42</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
         <v>43</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B13" t="s">
         <v>44</v>
       </c>
-      <c r="D11" t="s">
+      <c r="C13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" t="s">
         <v>45</v>
       </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
         <v>46</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B14" t="s">
         <v>47</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C14" t="s">
         <v>48</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D14" t="s">
         <v>49</v>
       </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
         <v>50</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B15" t="s">
         <v>51</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C15" t="s">
         <v>52</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D15" t="s">
         <v>53</v>
       </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
         <v>54</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B16" t="s">
         <v>55</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C16" t="s">
         <v>56</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D16" t="s">
         <v>57</v>
       </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
         <v>58</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B17" t="s">
         <v>59</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C17" t="s">
         <v>60</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D17" t="s">
         <v>61</v>
       </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
         <v>62</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B18" t="s">
         <v>63</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C18" t="s">
         <v>64</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D18" t="s">
         <v>65</v>
       </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
         <v>66</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B19" t="s">
         <v>67</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C19" t="s">
         <v>68</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D19" t="s">
         <v>69</v>
       </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>74</v>
-      </c>
-      <c r="B19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" t="s">
-        <v>76</v>
-      </c>
-      <c r="D19" t="s">
-        <v>77</v>
-      </c>
       <c r="E19" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>